--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ALABAMA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ALABAMA_2022.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C81">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C116">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C196">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C202">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C511">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C531">
